--- a/artfynd/A 27390-2025 artfynd.xlsx
+++ b/artfynd/A 27390-2025 artfynd.xlsx
@@ -680,11 +680,6 @@
       <c r="B2" t="n">
         <v>5175</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
       <c r="D2" t="inlineStr">
         <is>
           <t>NT</t>
@@ -795,7 +790,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Cecilia Backe, Susanna Isberg, Maria Sandell, Anna Fohrman, Jenny Hall, David Göransson, Johan Johnmark, Gunilla Davidsson Lundh, Kristian Nilsson, Alex Regnér</t>
+          <t>Alex Regnér, Kristian Nilsson, Gunilla Davidsson Lundh, Johan Johnmark, David Göransson, Jenny Hall, Anna Fohrman, Maria Sandell, Susanna Isberg, Cecilia Backe</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>

--- a/artfynd/A 27390-2025 artfynd.xlsx
+++ b/artfynd/A 27390-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125021756</v>
+        <v>125021778</v>
       </c>
       <c r="B2" t="n">
-        <v>5175</v>
+        <v>75428</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,32 +686,26 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102204</v>
+        <v>6426</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Grönhjon</t>
+          <t>Kattfotslav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Callidium aeneum</t>
+          <t>Felipes leucopellaeus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(De Geer, 1775)</t>
+          <t>(Ach.) Frisch &amp; G.Thor</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -719,13 +713,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>428498</v>
+        <v>428496</v>
       </c>
       <c r="R2" t="n">
-        <v>6234696</v>
+        <v>6234728</v>
       </c>
       <c r="S2" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -767,19 +761,24 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>Brantskog</t>
+        </is>
+      </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>rönn</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Sorbus aucuparia</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -794,6 +793,249 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>125021756</v>
+      </c>
+      <c r="B3" t="n">
+        <v>5178</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102204</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Grönhjon</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Callidium aeneum</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(De Geer, 1775)</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>S Pinkatorpet, Sk</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>428498</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6234696</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Stoby</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Alex Regnér, Kristian Nilsson, Gunilla Davidsson Lundh, Johan Johnmark, David Göransson, Jenny Hall, Anna Fohrman, Maria Sandell, Susanna Isberg, Cecilia Backe</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125021783</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80992</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>230185</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Havstulpanlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Thelotrema lepadinum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>S Pinkatorpet, Sk</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>428496</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6234728</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Hässleholm</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Stoby</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-05-12</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>Brantskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>rönn</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Sorbus aucuparia</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Alex Regnér</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Alex Regnér, Kristian Nilsson, Gunilla Davidsson Lundh, Johan Johnmark, David Göransson, Jenny Hall, Anna Fohrman, Maria Sandell, Susanna Isberg, Cecilia Backe</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27390-2025 artfynd.xlsx
+++ b/artfynd/A 27390-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -793,6 +798,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125021778</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -915,6 +925,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125021756</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1036,8 +1051,18 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125021783</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>